--- a/api_v3.xlsx
+++ b/api_v3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://integralogisticacol-my.sharepoint.com/personal/edwin_zarate_integralogistica_com/Documents/Desarrollos/integra/integrappi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{DA1A2ECD-1B99-4826-A79C-C16A61878527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFA9A495-E0BB-4ADC-AE50-A2A70FEBE7F2}"/>
+  <xr:revisionPtr revIDLastSave="79" documentId="8_{DA1A2ECD-1B99-4826-A79C-C16A61878527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A95C0E1-3E04-43A4-8225-3E0E68756C10}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5D375D6A-A91D-4E2F-9259-0D7D281510B3}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,62 +39,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="34">
-  <si>
-    <t>POR PROGRAMAR</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="49">
   <si>
     <t>CO07</t>
   </si>
   <si>
-    <t>CHISCAS</t>
-  </si>
-  <si>
-    <t>SOCOTA</t>
-  </si>
-  <si>
-    <t>PANQUEBA</t>
-  </si>
-  <si>
-    <t>CHITA</t>
-  </si>
-  <si>
-    <t>SOATA</t>
-  </si>
-  <si>
-    <t>LA UVITA</t>
-  </si>
-  <si>
-    <t>Casa 5 Vereda Barrio Las Palmas</t>
-  </si>
-  <si>
-    <t>Conjunto La 40 Casa 7 Via Tocaima</t>
-  </si>
-  <si>
-    <t>Calle 8 C #92-72 casa 199, Ciudad Tintal, súper manzana 5, super lote 1</t>
-  </si>
-  <si>
-    <t>KL 11 VIA CARMEN DE APICALA CONJUN</t>
-  </si>
-  <si>
-    <t>CLL 6 NO. 8-20 Barrio Centro Parroq</t>
-  </si>
-  <si>
     <t>R120</t>
   </si>
   <si>
-    <t>SERAFIN EMILIO REYES PINTO SERAFIN,EMILI</t>
-  </si>
-  <si>
-    <t>VANEGAS MARROQUIN LUIS ALBERTO</t>
-  </si>
-  <si>
-    <t>ORLANDO SILVA GOYENECHE ORLANDO, SILVA,</t>
-  </si>
-  <si>
-    <t>JAIRO VIDAL MORALES BELTRAN JAIRO,VIDAL</t>
-  </si>
-  <si>
     <t>Codigo Pedido</t>
   </si>
   <si>
@@ -137,17 +89,110 @@
     <t>Municipio Destino</t>
   </si>
   <si>
-    <t>CALLE 38 C SUR 89 C 21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EDWIN </t>
+    <t>Fecha Entrega</t>
+  </si>
+  <si>
+    <t>planilla</t>
+  </si>
+  <si>
+    <t>1235A</t>
+  </si>
+  <si>
+    <t>Davita Colombia S.A.S U.R. Duitama</t>
+  </si>
+  <si>
+    <t>Calle 9 # 36 - 24 Barrio Sausalito</t>
+  </si>
+  <si>
+    <t>0000-00-00</t>
+  </si>
+  <si>
+    <t>No Entregado</t>
+  </si>
+  <si>
+    <t>R126</t>
+  </si>
+  <si>
+    <t>DUITAMA</t>
+  </si>
+  <si>
+    <t>OLGA PATRICIA GRISALES BLANDON</t>
+  </si>
+  <si>
+    <t>CALLE 4 # 1- 40 BARRIO OBRERO</t>
+  </si>
+  <si>
+    <t>CO05</t>
+  </si>
+  <si>
+    <t>SALAMINA</t>
+  </si>
+  <si>
+    <t>SANDRA PATRICIA CAMPIÑO BALLESTEROS SAND</t>
+  </si>
+  <si>
+    <t>VEREDA COLORADOS, FINCA CIPRÃ‰S</t>
+  </si>
+  <si>
+    <t>MAYRA ALEJANDRA GIRALDO OSORIO MAYRA,ALE</t>
+  </si>
+  <si>
+    <t>CRA 11M-13 CASA 7 BARRIO LAS VEGAS</t>
+  </si>
+  <si>
+    <t>RE-651</t>
+  </si>
+  <si>
+    <t>DOSQUEBRADAS</t>
+  </si>
+  <si>
+    <t>Vantive S.A.S Girardot</t>
+  </si>
+  <si>
+    <t>Carrera 8a No. 20a-01 Barrio Granada N/A</t>
+  </si>
+  <si>
+    <t>GIRARDOT</t>
+  </si>
+  <si>
+    <t>VANTIVE AGENCIA SOACHA</t>
+  </si>
+  <si>
+    <t>Kra 7 # 47 - 35</t>
+  </si>
+  <si>
+    <t>SOACHA</t>
+  </si>
+  <si>
+    <t>divipola</t>
+  </si>
+  <si>
+    <t>ENTREGADO</t>
+  </si>
+  <si>
+    <t>POR CONFIRMAR</t>
+  </si>
+  <si>
+    <t>EDWIN ZARATE</t>
+  </si>
+  <si>
+    <t>CALLE 28 CE SUR NO 89 C 21</t>
+  </si>
+  <si>
+    <t>SIN PROGRAMAR</t>
+  </si>
+  <si>
+    <t>BOGOTA</t>
+  </si>
+  <si>
+    <t>311 5956621</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -162,8 +207,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -176,8 +227,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -200,16 +257,69 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -544,7 +654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AF80A5B-70DA-4E78-8BE2-AD728ABA29F9}">
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -553,320 +663,474 @@
     <col min="4" max="4" width="42.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="11.6640625" customWidth="1"/>
+    <col min="11" max="11" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="21.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>3536763690</v>
+      </c>
+      <c r="B2" s="2">
+        <v>920229974</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="2">
+        <v>15238000</v>
+      </c>
+      <c r="F2" s="7">
+        <v>3208606921</v>
+      </c>
+      <c r="G2" s="3">
+        <v>46113.425173611111</v>
+      </c>
+      <c r="H2" s="4">
+        <v>46097</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="2"/>
+      <c r="K2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="5">
+        <v>12</v>
+      </c>
+      <c r="M2" s="5">
+        <v>396</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" s="5">
+        <v>15238000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>3536930155</v>
+      </c>
+      <c r="B3" s="2">
+        <v>930577955</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="2">
+        <v>17653000</v>
+      </c>
+      <c r="F3" s="2">
+        <v>3123418728</v>
+      </c>
+      <c r="G3" s="3">
+        <v>46113.456863425927</v>
+      </c>
+      <c r="H3" s="4">
+        <v>46121</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="K3" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>17653000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>3536930248</v>
+      </c>
+      <c r="B4" s="2">
+        <v>970033269</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="2">
+        <v>17653000</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="3">
+        <v>46113.456990740742</v>
+      </c>
+      <c r="H4" s="4">
+        <v>46121</v>
+      </c>
+      <c r="I4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="J4" s="2">
+        <v>1234</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>17653000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>3536930938</v>
+      </c>
+      <c r="B5" s="2">
+        <v>970250066</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="2">
+        <v>66170000</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>46119.345879629633</v>
+      </c>
+      <c r="H5" s="4">
+        <v>46121</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="2"/>
+      <c r="K5" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>66170000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>3536932399</v>
+      </c>
+      <c r="B6" s="2">
+        <v>920228018</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="2">
+        <v>25307000</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="3">
+        <v>46113.600960648146</v>
+      </c>
+      <c r="H6" s="4">
+        <v>46119</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="2"/>
+      <c r="K6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>31</v>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q6" s="5">
+        <v>25307000</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>3536647266</v>
-      </c>
-      <c r="B2">
-        <v>970304159</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2">
-        <v>15180000</v>
-      </c>
-      <c r="G2" s="2">
-        <v>46076</v>
-      </c>
-      <c r="H2" s="2">
-        <v>46093</v>
-      </c>
-      <c r="I2" t="s">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2" t="s">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>3536932439</v>
+      </c>
+      <c r="B7" s="2">
+        <v>920231208</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="2">
+        <v>25754000</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="3">
+        <v>46113.596354166664</v>
+      </c>
+      <c r="H7" s="4">
+        <v>46120</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="2"/>
+      <c r="K7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="O7" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="M2" t="s">
-        <v>13</v>
-      </c>
-      <c r="N2" t="s">
-        <v>2</v>
+      <c r="P7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>25754000</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>3536647249</v>
-      </c>
-      <c r="B3">
-        <v>970126269</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3">
-        <v>15755000</v>
-      </c>
-      <c r="F3">
-        <v>3115774510</v>
-      </c>
-      <c r="G3" s="2">
-        <v>46076</v>
-      </c>
-      <c r="H3" s="2">
-        <v>46093</v>
-      </c>
-      <c r="I3" t="s">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3" t="s">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>3536932520</v>
+      </c>
+      <c r="B8" s="2">
+        <v>920231208</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="2">
+        <v>25754000</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="3">
+        <v>46113.596875000003</v>
+      </c>
+      <c r="H8" s="4">
+        <v>46122</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="2"/>
+      <c r="K8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="O8" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="M3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N3" t="s">
-        <v>3</v>
+      <c r="P8" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>25754000</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3536647246</v>
-      </c>
-      <c r="B4">
-        <v>970289429</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4">
-        <v>15522000</v>
-      </c>
-      <c r="F4">
-        <v>3229135586</v>
-      </c>
-      <c r="G4" s="2">
-        <v>46076</v>
-      </c>
-      <c r="H4" s="2">
-        <v>46093</v>
-      </c>
-      <c r="I4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4" t="s">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>3536932523</v>
+      </c>
+      <c r="B9" s="2">
+        <v>920231208</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="2">
+        <v>25754000</v>
+      </c>
+      <c r="F9" s="8"/>
+      <c r="G9" s="3">
+        <v>46113.596875000003</v>
+      </c>
+      <c r="H9" s="4">
+        <v>46122</v>
+      </c>
+      <c r="I9" s="5"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="O9" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="M4" t="s">
-        <v>13</v>
-      </c>
-      <c r="N4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>3536647241</v>
-      </c>
-      <c r="B5">
-        <v>970304539</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5">
-        <v>15183000</v>
-      </c>
-      <c r="F5">
-        <v>3123557901</v>
-      </c>
-      <c r="G5" s="2">
-        <v>46076</v>
-      </c>
-      <c r="H5" s="2">
-        <v>46093</v>
-      </c>
-      <c r="I5" t="s">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5" t="s">
-        <v>1</v>
-      </c>
-      <c r="M5" t="s">
-        <v>13</v>
-      </c>
-      <c r="N5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>3536647236</v>
-      </c>
-      <c r="B6">
-        <v>970156315</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6">
-        <v>15753000</v>
-      </c>
-      <c r="F6">
-        <v>3226427403</v>
-      </c>
-      <c r="G6" s="2">
-        <v>46076</v>
-      </c>
-      <c r="H6" s="2">
-        <v>46093</v>
-      </c>
-      <c r="I6" t="s">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6" t="s">
-        <v>1</v>
-      </c>
-      <c r="M6" t="s">
-        <v>13</v>
-      </c>
-      <c r="N6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>3536647229</v>
-      </c>
-      <c r="B7">
-        <v>970267640</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7">
-        <v>15403000</v>
-      </c>
-      <c r="F7">
-        <v>3213756904</v>
-      </c>
-      <c r="G7" s="2">
-        <v>46076</v>
-      </c>
-      <c r="H7" s="2">
-        <v>46093</v>
-      </c>
-      <c r="I7" t="s">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M7" t="s">
-        <v>13</v>
-      </c>
-      <c r="N7" t="s">
-        <v>7</v>
+      <c r="P9" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>25754001</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N7" xr:uid="{4AF80A5B-70DA-4E78-8BE2-AD728ABA29F9}"/>
+  <autoFilter ref="A1:P7" xr:uid="{4AF80A5B-70DA-4E78-8BE2-AD728ABA29F9}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
